--- a/igrejas.xlsx
+++ b/igrejas.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="1016">
   <si>
     <t>NOME</t>
   </si>
@@ -378,9 +378,6 @@
     <t>Capela Nossa Senhora Imaculada da Conceição</t>
   </si>
   <si>
-    <t>Rua Girinaldo Batista, 2818</t>
-  </si>
-  <si>
     <t>Acarape</t>
   </si>
   <si>
@@ -426,9 +423,6 @@
     <t>_paroquiasantissimatrindade</t>
   </si>
   <si>
-    <t>ParóquiaSantíssimaTrindadeTeresina</t>
-  </si>
-  <si>
     <t>Igreja Nossa Senhora da Esperança</t>
   </si>
   <si>
@@ -472,9 +466,6 @@
   </si>
   <si>
     <t>paroquiasaopaulo_the</t>
-  </si>
-  <si>
-    <t>ParoquiaSãoPaulotv</t>
   </si>
   <si>
     <t>Capela de São Francisco</t>
@@ -2941,6 +2932,147 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/DKqUrsnYuj5HgEmn9</t>
+  </si>
+  <si>
+    <t>-5.0817194</t>
+  </si>
+  <si>
+    <t>-42.8250127</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/K5stpDC6FtjDLRKh7</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/capeladenossasenhoraaparecida/</t>
+  </si>
+  <si>
+    <t>-5.070148</t>
+  </si>
+  <si>
+    <t>-42.824473</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/G5gWywwUHwDLmrVf8</t>
+  </si>
+  <si>
+    <t>Rua Rui Lima, 2821</t>
+  </si>
+  <si>
+    <t>-5.0703323</t>
+  </si>
+  <si>
+    <t>-42.8352057</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3bEZoGcDPmadBLX5A</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/capelade.santoafonso/</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/HW2WYma8jT6q6Mem6</t>
+  </si>
+  <si>
+    <t>-5.0678946</t>
+  </si>
+  <si>
+    <t>-42.8313401</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/YhXTycwUCiGj1aQQ7</t>
+  </si>
+  <si>
+    <t>-5.0641887</t>
+  </si>
+  <si>
+    <t>-42.8316477</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/santissimatrindad/?locale=pt_BR</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/vYhvyQnrQXSRPKcc7</t>
+  </si>
+  <si>
+    <t>-5.067617</t>
+  </si>
+  <si>
+    <t>-42.8128567</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/Par%C3%B3quiaSant%C3%ADssimaTrindadeTeresina</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BtBwu2oTfJaJGpqH9</t>
+  </si>
+  <si>
+    <t>-42.8075267</t>
+  </si>
+  <si>
+    <t>-5.0711428</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mNRunJwHwe8wJYMM8</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/csaomanuel/</t>
+  </si>
+  <si>
+    <t>-5.0591351</t>
+  </si>
+  <si>
+    <t>-42.8130911</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3sM7dwKcGX8T2kzP8</t>
+  </si>
+  <si>
+    <t>-42.8156273</t>
+  </si>
+  <si>
+    <t>-5.0603716</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/ParoquiaS%C3%A3oPaulotv</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Par%C3%B3quia+S%C3%A3o+Paulo/@-5.0375919,-42.8156958,762m/data=!3m2!1e3!4b1!4m6!3m5!1s0x78e3923465c7627:0x2986c8e959a5650!8m2!3d-5.0375919!4d-42.8156958!16s%2Fg%2F1ptysh8vw?entry=tts&amp;g_ep=EgoyMDI2MDUwMi4wIPu8ASoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>-5.0375919</t>
+  </si>
+  <si>
+    <t>-42.8156958</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Na6Kg7btC4YBbUNV9</t>
+  </si>
+  <si>
+    <t>-5.0325639</t>
+  </si>
+  <si>
+    <t>-42.8222525</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WfM8DXkZHLYZ2Ekw9</t>
+  </si>
+  <si>
+    <t>-42.8167244</t>
+  </si>
+  <si>
+    <t>-5.0332131</t>
+  </si>
+  <si>
+    <t>-5.041765</t>
+  </si>
+  <si>
+    <t>-42.8121737</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rvEYZbWpBCHM8piG7</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1Z5urh1WtHdsUtbS8</t>
   </si>
 </sst>
 </file>
@@ -3729,7 +3861,7 @@
         <v>26</v>
       </c>
       <c r="O2" s="59" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="P2" s="15" t="s">
         <v>27</v>
@@ -3781,10 +3913,10 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="60" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="O3" s="60" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="P3" s="65" t="s">
         <v>31</v>
@@ -3844,10 +3976,10 @@
       </c>
       <c r="M4" s="79"/>
       <c r="N4" s="84" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="O4" s="84" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="P4" s="85" t="s">
         <v>40</v>
@@ -3905,10 +4037,10 @@
       <c r="L5" s="79"/>
       <c r="M5" s="79"/>
       <c r="N5" s="88" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="O5" s="84" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="P5" s="85" t="s">
         <v>47</v>
@@ -3964,17 +4096,17 @@
         <v>54</v>
       </c>
       <c r="L6" s="76" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="M6" s="71"/>
       <c r="N6" s="77" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="O6" s="77" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="P6" s="76" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="Q6" s="78">
         <v>86988061508</v>
@@ -4020,7 +4152,7 @@
         <v>58</v>
       </c>
       <c r="I7" s="65" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="J7" s="22"/>
       <c r="K7" s="18" t="s">
@@ -4029,13 +4161,13 @@
       <c r="L7" s="22"/>
       <c r="M7" s="22"/>
       <c r="N7" s="60" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="O7" s="60" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="P7" s="65" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="Q7" s="25">
         <v>86994299055</v>
@@ -4088,17 +4220,17 @@
         <v>66</v>
       </c>
       <c r="L8" s="67" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="M8" s="32"/>
       <c r="N8" s="68" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="O8" s="68" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="P8" s="67" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="Q8" s="63">
         <v>86995413427</v>
@@ -4137,7 +4269,9 @@
       <c r="F9" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="42" t="s">
+        <v>63</v>
+      </c>
       <c r="H9" s="20"/>
       <c r="I9" s="21"/>
       <c r="J9" s="22"/>
@@ -4147,13 +4281,13 @@
       <c r="L9" s="22"/>
       <c r="M9" s="22"/>
       <c r="N9" s="60" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="O9" s="60" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="P9" s="65" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="Q9" s="63"/>
       <c r="R9" s="37"/>
@@ -4190,7 +4324,9 @@
       <c r="F10" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="42" t="s">
+        <v>63</v>
+      </c>
       <c r="H10" s="20"/>
       <c r="I10" s="21"/>
       <c r="J10" s="22"/>
@@ -4200,13 +4336,13 @@
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
       <c r="N10" s="60" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="O10" s="60" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="P10" s="65" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="Q10" s="63"/>
       <c r="R10" s="37"/>
@@ -4243,7 +4379,9 @@
       <c r="F11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="22"/>
+      <c r="G11" s="42" t="s">
+        <v>63</v>
+      </c>
       <c r="H11" s="20"/>
       <c r="I11" s="21"/>
       <c r="J11" s="22"/>
@@ -4253,13 +4391,13 @@
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
       <c r="N11" s="60" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="P11" s="65" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="Q11" s="63"/>
       <c r="R11" s="37"/>
@@ -4312,13 +4450,13 @@
       <c r="L12" s="32"/>
       <c r="M12" s="32"/>
       <c r="N12" s="68" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="O12" s="68" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="P12" s="67" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="Q12" s="63"/>
       <c r="R12" s="37"/>
@@ -4373,13 +4511,13 @@
       </c>
       <c r="M13" s="32"/>
       <c r="N13" s="68" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="O13" s="68" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="P13" s="67" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="Q13" s="63"/>
       <c r="R13" s="37"/>
@@ -4430,13 +4568,13 @@
       <c r="L14" s="32"/>
       <c r="M14" s="32"/>
       <c r="N14" s="68" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="O14" s="68" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="P14" s="67" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="Q14" s="63"/>
       <c r="R14" s="37"/>
@@ -4487,13 +4625,13 @@
       <c r="L15" s="32"/>
       <c r="M15" s="32"/>
       <c r="N15" s="68" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="O15" s="68" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="P15" s="67" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="Q15" s="63"/>
       <c r="R15" s="37"/>
@@ -4546,19 +4684,19 @@
         <v>108</v>
       </c>
       <c r="L16" s="67" t="s">
+        <v>964</v>
+      </c>
+      <c r="M16" s="67" t="s">
+        <v>965</v>
+      </c>
+      <c r="N16" s="68" t="s">
+        <v>966</v>
+      </c>
+      <c r="O16" s="68" t="s">
         <v>967</v>
       </c>
-      <c r="M16" s="67" t="s">
+      <c r="P16" s="67" t="s">
         <v>968</v>
-      </c>
-      <c r="N16" s="68" t="s">
-        <v>969</v>
-      </c>
-      <c r="O16" s="68" t="s">
-        <v>970</v>
-      </c>
-      <c r="P16" s="67" t="s">
-        <v>971</v>
       </c>
       <c r="Q16" s="63">
         <v>86988022779</v>
@@ -4591,20 +4729,34 @@
       <c r="D17" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="22"/>
+      <c r="E17" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>104</v>
+      </c>
       <c r="H17" s="20"/>
       <c r="I17" s="21"/>
       <c r="J17" s="21"/>
       <c r="K17" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L17" s="22"/>
+      <c r="L17" s="65" t="s">
+        <v>972</v>
+      </c>
       <c r="M17" s="22"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="22"/>
+      <c r="N17" s="60" t="s">
+        <v>969</v>
+      </c>
+      <c r="O17" s="60" t="s">
+        <v>970</v>
+      </c>
+      <c r="P17" s="65" t="s">
+        <v>971</v>
+      </c>
       <c r="Q17" s="63"/>
       <c r="R17" s="37"/>
       <c r="S17" s="37"/>
@@ -4634,9 +4786,15 @@
       <c r="D18" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>104</v>
+      </c>
       <c r="H18" s="20"/>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
@@ -4645,9 +4803,15 @@
       </c>
       <c r="L18" s="22"/>
       <c r="M18" s="22"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="22"/>
+      <c r="N18" s="60" t="s">
+        <v>973</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>974</v>
+      </c>
+      <c r="P18" s="65" t="s">
+        <v>975</v>
+      </c>
       <c r="Q18" s="63"/>
       <c r="R18" s="37"/>
       <c r="S18" s="37"/>
@@ -4668,29 +4832,41 @@
       <c r="A19" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="70" t="s">
+        <v>976</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>118</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>119</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>104</v>
+      </c>
       <c r="H19" s="20"/>
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
       <c r="K19" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L19" s="22"/>
       <c r="M19" s="22"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="22"/>
+      <c r="N19" s="60" t="s">
+        <v>977</v>
+      </c>
+      <c r="O19" s="60" t="s">
+        <v>978</v>
+      </c>
+      <c r="P19" s="65" t="s">
+        <v>979</v>
+      </c>
       <c r="Q19" s="63"/>
       <c r="R19" s="37"/>
       <c r="S19" s="37"/>
@@ -4709,10 +4885,10 @@
     </row>
     <row r="20" spans="1:31" ht="15.75" customHeight="1">
       <c r="A20" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>121</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>122</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>115</v>
@@ -4720,20 +4896,34 @@
       <c r="D20" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>104</v>
+      </c>
       <c r="H20" s="20"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="L20" s="22"/>
+        <v>122</v>
+      </c>
+      <c r="L20" s="65" t="s">
+        <v>980</v>
+      </c>
       <c r="M20" s="22"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="22"/>
+      <c r="N20" s="60" t="s">
+        <v>982</v>
+      </c>
+      <c r="O20" s="60" t="s">
+        <v>983</v>
+      </c>
+      <c r="P20" s="65" t="s">
+        <v>981</v>
+      </c>
       <c r="Q20" s="63"/>
       <c r="R20" s="37"/>
       <c r="S20" s="37"/>
@@ -4752,10 +4942,10 @@
     </row>
     <row r="21" spans="1:31" ht="15.75" customHeight="1">
       <c r="A21" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>124</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>125</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>115</v>
@@ -4763,20 +4953,32 @@
       <c r="D21" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>104</v>
+      </c>
       <c r="H21" s="20"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
       <c r="K21" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="39"/>
-      <c r="P21" s="22"/>
+      <c r="N21" s="60" t="s">
+        <v>985</v>
+      </c>
+      <c r="O21" s="60" t="s">
+        <v>986</v>
+      </c>
+      <c r="P21" s="22" t="s">
+        <v>984</v>
+      </c>
       <c r="Q21" s="63"/>
       <c r="R21" s="37"/>
       <c r="S21" s="37"/>
@@ -4795,40 +4997,54 @@
     </row>
     <row r="22" spans="1:31" ht="15.75" customHeight="1">
       <c r="A22" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="C22" s="32" t="s">
         <v>128</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>129</v>
       </c>
       <c r="D22" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
+      <c r="E22" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="66" t="s">
+        <v>20</v>
+      </c>
       <c r="G22" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="I22" s="35" t="s">
         <v>131</v>
-      </c>
-      <c r="I22" s="35" t="s">
-        <v>132</v>
       </c>
       <c r="J22" s="32"/>
       <c r="K22" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="63"/>
+        <v>132</v>
+      </c>
+      <c r="L22" s="67" t="s">
+        <v>987</v>
+      </c>
+      <c r="M22" s="67" t="s">
+        <v>991</v>
+      </c>
+      <c r="N22" s="68" t="s">
+        <v>989</v>
+      </c>
+      <c r="O22" s="68" t="s">
+        <v>990</v>
+      </c>
+      <c r="P22" s="32" t="s">
+        <v>988</v>
+      </c>
+      <c r="Q22" s="63">
+        <v>8630851310</v>
+      </c>
       <c r="R22" s="37"/>
       <c r="S22" s="37"/>
       <c r="T22" s="37"/>
@@ -4846,31 +5062,43 @@
     </row>
     <row r="23" spans="1:31" ht="15.75" customHeight="1">
       <c r="A23" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="18" t="s">
         <v>135</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>137</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="22"/>
+      <c r="E23" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>129</v>
+      </c>
       <c r="H23" s="20"/>
       <c r="I23" s="21"/>
       <c r="J23" s="22"/>
       <c r="K23" s="18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="22"/>
+      <c r="N23" s="60" t="s">
+        <v>994</v>
+      </c>
+      <c r="O23" s="60" t="s">
+        <v>993</v>
+      </c>
+      <c r="P23" s="22" t="s">
+        <v>992</v>
+      </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="37"/>
       <c r="S23" s="37"/>
@@ -4889,29 +5117,43 @@
     </row>
     <row r="24" spans="1:31" ht="15.75" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="22"/>
+      <c r="E24" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>129</v>
+      </c>
       <c r="H24" s="20"/>
       <c r="I24" s="21"/>
       <c r="J24" s="22"/>
       <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="L24" s="22" t="s">
+        <v>996</v>
+      </c>
       <c r="M24" s="22"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="22"/>
+      <c r="N24" s="60" t="s">
+        <v>997</v>
+      </c>
+      <c r="O24" s="60" t="s">
+        <v>998</v>
+      </c>
+      <c r="P24" s="22" t="s">
+        <v>995</v>
+      </c>
       <c r="Q24" s="63"/>
       <c r="R24" s="37"/>
       <c r="S24" s="37"/>
@@ -4930,29 +5172,41 @@
     </row>
     <row r="25" spans="1:31" ht="15.75" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="22"/>
+      <c r="E25" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>129</v>
+      </c>
       <c r="H25" s="20"/>
       <c r="I25" s="21"/>
       <c r="J25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
       <c r="M25" s="22"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="39"/>
-      <c r="P25" s="22"/>
+      <c r="N25" s="60" t="s">
+        <v>1001</v>
+      </c>
+      <c r="O25" s="60" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P25" s="65" t="s">
+        <v>999</v>
+      </c>
       <c r="Q25" s="63"/>
       <c r="R25" s="37"/>
       <c r="S25" s="37"/>
@@ -4971,40 +5225,52 @@
     </row>
     <row r="26" spans="1:31" ht="15.75" customHeight="1">
       <c r="A26" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="32" t="s">
         <v>143</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>145</v>
       </c>
       <c r="D26" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+      <c r="E26" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>20</v>
+      </c>
       <c r="G26" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="I26" s="35" t="s">
         <v>146</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="I26" s="35" t="s">
-        <v>148</v>
       </c>
       <c r="J26" s="32"/>
       <c r="K26" s="32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L26" s="32"/>
-      <c r="M26" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="63"/>
+      <c r="M26" s="67" t="s">
+        <v>1002</v>
+      </c>
+      <c r="N26" s="68" t="s">
+        <v>1004</v>
+      </c>
+      <c r="O26" s="68" t="s">
+        <v>1005</v>
+      </c>
+      <c r="P26" s="32" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Q26" s="63">
+        <v>86998296280</v>
+      </c>
       <c r="R26" s="37"/>
       <c r="S26" s="37"/>
       <c r="T26" s="37"/>
@@ -5022,33 +5288,45 @@
     </row>
     <row r="27" spans="1:31" ht="15.75" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="22"/>
+      <c r="E27" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>144</v>
+      </c>
       <c r="H27" s="38" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="22"/>
-      <c r="K27" s="18" t="s">
-        <v>155</v>
+      <c r="K27" s="70" t="s">
+        <v>152</v>
       </c>
       <c r="L27" s="22"/>
       <c r="M27" s="22"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="39"/>
-      <c r="P27" s="22"/>
+      <c r="N27" s="60" t="s">
+        <v>1007</v>
+      </c>
+      <c r="O27" s="60" t="s">
+        <v>1008</v>
+      </c>
+      <c r="P27" s="22" t="s">
+        <v>1006</v>
+      </c>
       <c r="Q27" s="63"/>
       <c r="R27" s="37"/>
       <c r="S27" s="37"/>
@@ -5070,28 +5348,40 @@
         <v>71</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="22"/>
+      <c r="E28" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>144</v>
+      </c>
       <c r="H28" s="20"/>
       <c r="I28" s="21"/>
       <c r="J28" s="22"/>
       <c r="K28" s="18" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L28" s="22"/>
       <c r="M28" s="22"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="39"/>
-      <c r="P28" s="22"/>
+      <c r="N28" s="60" t="s">
+        <v>1011</v>
+      </c>
+      <c r="O28" s="60" t="s">
+        <v>1010</v>
+      </c>
+      <c r="P28" s="22" t="s">
+        <v>1009</v>
+      </c>
       <c r="Q28" s="63"/>
       <c r="R28" s="37"/>
       <c r="S28" s="37"/>
@@ -5110,31 +5400,43 @@
     </row>
     <row r="29" spans="1:31" ht="15.75" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="22"/>
+      <c r="E29" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>144</v>
+      </c>
       <c r="H29" s="20"/>
       <c r="I29" s="21"/>
       <c r="J29" s="22"/>
       <c r="K29" s="18" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="22"/>
+      <c r="N29" s="60" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O29" s="60" t="s">
+        <v>1013</v>
+      </c>
+      <c r="P29" s="65" t="s">
+        <v>1014</v>
+      </c>
       <c r="Q29" s="63"/>
       <c r="R29" s="37"/>
       <c r="S29" s="37"/>
@@ -5153,31 +5455,43 @@
     </row>
     <row r="30" spans="1:31" ht="15.75" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="22"/>
+      <c r="E30" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>144</v>
+      </c>
       <c r="H30" s="20"/>
       <c r="I30" s="21"/>
       <c r="J30" s="22"/>
       <c r="K30" s="18" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="22"/>
+      <c r="N30" s="60" t="s">
+        <v>1004</v>
+      </c>
+      <c r="O30" s="60" t="s">
+        <v>1005</v>
+      </c>
+      <c r="P30" s="65" t="s">
+        <v>1015</v>
+      </c>
       <c r="Q30" s="63"/>
       <c r="R30" s="37"/>
       <c r="S30" s="37"/>
@@ -5196,13 +5510,13 @@
     </row>
     <row r="31" spans="1:31" ht="15.75" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>20</v>
@@ -5210,22 +5524,22 @@
       <c r="E31" s="33"/>
       <c r="F31" s="33"/>
       <c r="G31" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="J31" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="H31" s="34" t="s">
+      <c r="K31" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="I31" s="35" t="s">
+      <c r="L31" s="32" t="s">
         <v>170</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="K31" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="L31" s="32" t="s">
-        <v>173</v>
       </c>
       <c r="M31" s="32"/>
       <c r="N31" s="36"/>
@@ -5249,13 +5563,13 @@
     </row>
     <row r="32" spans="1:31" ht="15.75" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>21</v>
@@ -5267,7 +5581,7 @@
       <c r="I32" s="21"/>
       <c r="J32" s="18"/>
       <c r="K32" s="18" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
@@ -5292,13 +5606,13 @@
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>21</v>
@@ -5307,12 +5621,12 @@
       <c r="F33" s="19"/>
       <c r="G33" s="22"/>
       <c r="H33" s="20" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I33" s="21"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
@@ -5337,13 +5651,13 @@
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>21</v>
@@ -5355,7 +5669,7 @@
       <c r="I34" s="21"/>
       <c r="J34" s="18"/>
       <c r="K34" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
@@ -5380,13 +5694,13 @@
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>21</v>
@@ -5398,7 +5712,7 @@
       <c r="I35" s="21"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
@@ -5423,13 +5737,13 @@
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1">
       <c r="A36" s="42" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D36" s="33" t="s">
         <v>20</v>
@@ -5437,20 +5751,20 @@
       <c r="E36" s="33"/>
       <c r="F36" s="33"/>
       <c r="G36" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H36" s="34" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I36" s="35" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J36" s="32"/>
       <c r="K36" s="32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="L36" s="32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M36" s="32"/>
       <c r="N36" s="36"/>
@@ -5474,10 +5788,10 @@
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="19" t="s">
@@ -5488,7 +5802,7 @@
       <c r="G37" s="22"/>
       <c r="H37" s="20"/>
       <c r="I37" s="43" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J37" s="22"/>
       <c r="K37" s="22"/>
@@ -5515,7 +5829,7 @@
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
@@ -5552,10 +5866,10 @@
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>115</v>
@@ -5568,10 +5882,10 @@
       <c r="G39" s="22"/>
       <c r="H39" s="20"/>
       <c r="I39" s="43" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J39" s="24" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
@@ -5600,10 +5914,10 @@
         <v>74</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>21</v>
@@ -5638,13 +5952,13 @@
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D41" s="33" t="s">
         <v>20</v>
@@ -5652,23 +5966,23 @@
       <c r="E41" s="33"/>
       <c r="F41" s="33"/>
       <c r="G41" s="32" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H41" s="34" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I41" s="35" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J41" s="32"/>
       <c r="K41" s="32" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L41" s="32" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M41" s="32" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N41" s="36"/>
       <c r="O41" s="36"/>
@@ -5691,13 +6005,13 @@
     </row>
     <row r="42" spans="1:31" ht="15.75" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>21</v>
@@ -5709,7 +6023,7 @@
       <c r="I42" s="21"/>
       <c r="J42" s="22"/>
       <c r="K42" s="18" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L42" s="22"/>
       <c r="M42" s="22"/>
@@ -5734,13 +6048,13 @@
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>21</v>
@@ -5752,7 +6066,7 @@
       <c r="I43" s="21"/>
       <c r="J43" s="22"/>
       <c r="K43" s="18" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L43" s="22"/>
       <c r="M43" s="22"/>
@@ -5777,13 +6091,13 @@
     </row>
     <row r="44" spans="1:31" ht="15.75" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>21</v>
@@ -5795,7 +6109,7 @@
       <c r="I44" s="21"/>
       <c r="J44" s="22"/>
       <c r="K44" s="18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L44" s="22"/>
       <c r="M44" s="22"/>
@@ -5820,7 +6134,7 @@
     </row>
     <row r="45" spans="1:31" ht="15.75" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
@@ -5857,13 +6171,13 @@
     </row>
     <row r="46" spans="1:31" ht="15.75" customHeight="1">
       <c r="A46" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D46" s="28" t="s">
         <v>20</v>
@@ -5871,23 +6185,23 @@
       <c r="E46" s="28"/>
       <c r="F46" s="28"/>
       <c r="G46" s="27" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I46" s="31" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J46" s="27"/>
       <c r="K46" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L46" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M46" s="44" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N46" s="45"/>
       <c r="O46" s="45"/>
@@ -5910,13 +6224,13 @@
     </row>
     <row r="47" spans="1:31" ht="15.75" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>21</v>
@@ -5924,15 +6238,15 @@
       <c r="E47" s="19"/>
       <c r="F47" s="19"/>
       <c r="G47" s="22" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I47" s="21"/>
       <c r="J47" s="22"/>
       <c r="K47" s="18" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L47" s="22"/>
       <c r="M47" s="46"/>
@@ -5957,13 +6271,13 @@
     </row>
     <row r="48" spans="1:31" ht="15.75" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>21</v>
@@ -5975,7 +6289,7 @@
       <c r="I48" s="21"/>
       <c r="J48" s="22"/>
       <c r="K48" s="18" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="L48" s="22"/>
       <c r="M48" s="46"/>
@@ -6000,13 +6314,13 @@
     </row>
     <row r="49" spans="1:31" ht="15.75" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>21</v>
@@ -6018,7 +6332,7 @@
       <c r="I49" s="21"/>
       <c r="J49" s="22"/>
       <c r="K49" s="18" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L49" s="22"/>
       <c r="M49" s="46"/>
@@ -6043,13 +6357,13 @@
     </row>
     <row r="50" spans="1:31" ht="15.75" customHeight="1">
       <c r="A50" s="18" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>21</v>
@@ -6061,7 +6375,7 @@
       <c r="I50" s="21"/>
       <c r="J50" s="22"/>
       <c r="K50" s="18" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="L50" s="22"/>
       <c r="M50" s="46"/>
@@ -6086,13 +6400,13 @@
     </row>
     <row r="51" spans="1:31" ht="15.75" customHeight="1">
       <c r="A51" s="32" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B51" s="42" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D51" s="33" t="s">
         <v>20</v>
@@ -6100,21 +6414,21 @@
       <c r="E51" s="33"/>
       <c r="F51" s="33"/>
       <c r="G51" s="32" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H51" s="34" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I51" s="35" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J51" s="32"/>
       <c r="K51" s="32" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L51" s="32"/>
       <c r="M51" s="32" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N51" s="36"/>
       <c r="O51" s="36"/>
@@ -6137,13 +6451,13 @@
     </row>
     <row r="52" spans="1:31" ht="15.75" customHeight="1">
       <c r="A52" s="18" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D52" s="48" t="s">
         <v>21</v>
@@ -6155,11 +6469,11 @@
       <c r="I52" s="21"/>
       <c r="J52" s="22"/>
       <c r="K52" s="18" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L52" s="22"/>
       <c r="M52" s="18" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="N52" s="23"/>
       <c r="O52" s="39"/>
@@ -6182,13 +6496,13 @@
     </row>
     <row r="53" spans="1:31" ht="15.75" customHeight="1">
       <c r="A53" s="18" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D53" s="48" t="s">
         <v>21</v>
@@ -6197,12 +6511,12 @@
       <c r="F53" s="48"/>
       <c r="G53" s="22"/>
       <c r="H53" s="20" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I53" s="21"/>
       <c r="J53" s="22"/>
       <c r="K53" s="18" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="L53" s="22"/>
       <c r="M53" s="22"/>
@@ -6227,13 +6541,13 @@
     </row>
     <row r="54" spans="1:31" ht="15.75" customHeight="1">
       <c r="A54" s="32" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C54" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D54" s="33" t="s">
         <v>21</v>
@@ -6242,7 +6556,7 @@
       <c r="F54" s="33"/>
       <c r="G54" s="32"/>
       <c r="H54" s="49" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I54" s="35" t="s">
         <v>88</v>
@@ -6276,10 +6590,10 @@
     </row>
     <row r="55" spans="1:31" ht="15.75" customHeight="1">
       <c r="A55" s="32" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B55" s="32" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C55" s="32" t="s">
         <v>50</v>
@@ -6293,7 +6607,7 @@
         <v>51</v>
       </c>
       <c r="H55" s="34" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I55" s="32"/>
       <c r="J55" s="32"/>
@@ -6321,13 +6635,13 @@
     </row>
     <row r="56" spans="1:31" ht="15.75" customHeight="1">
       <c r="A56" s="32" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D56" s="33" t="s">
         <v>21</v>
@@ -6335,7 +6649,7 @@
       <c r="E56" s="33"/>
       <c r="F56" s="33"/>
       <c r="G56" s="32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H56" s="34"/>
       <c r="I56" s="32"/>
@@ -6364,13 +6678,13 @@
     </row>
     <row r="57" spans="1:31" ht="15.75" customHeight="1">
       <c r="A57" s="32" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D57" s="33" t="s">
         <v>20</v>
@@ -6378,20 +6692,20 @@
       <c r="E57" s="33"/>
       <c r="F57" s="33"/>
       <c r="G57" s="32" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H57" s="34" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I57" s="35" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J57" s="32"/>
       <c r="K57" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L57" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M57" s="32"/>
       <c r="N57" s="36"/>
@@ -6415,13 +6729,13 @@
     </row>
     <row r="58" spans="1:31" ht="15.75" customHeight="1">
       <c r="A58" s="32" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C58" s="32" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D58" s="33" t="s">
         <v>20</v>
@@ -6429,23 +6743,23 @@
       <c r="E58" s="33"/>
       <c r="F58" s="33"/>
       <c r="G58" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H58" s="34" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I58" s="35" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J58" s="32"/>
       <c r="K58" s="32" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="L58" s="32" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="M58" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N58" s="36"/>
       <c r="O58" s="36"/>
@@ -6468,13 +6782,13 @@
     </row>
     <row r="59" spans="1:31" ht="15.75" customHeight="1">
       <c r="A59" s="32" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B59" s="32" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D59" s="33" t="s">
         <v>20</v>
@@ -6482,20 +6796,20 @@
       <c r="E59" s="33"/>
       <c r="F59" s="33"/>
       <c r="G59" s="32" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H59" s="34" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I59" s="35" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J59" s="32"/>
       <c r="K59" s="32" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="L59" s="32" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="M59" s="32"/>
       <c r="N59" s="36"/>
@@ -6519,13 +6833,13 @@
     </row>
     <row r="60" spans="1:31" ht="15.75" customHeight="1">
       <c r="A60" s="32" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B60" s="32" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D60" s="33" t="s">
         <v>20</v>
@@ -6533,23 +6847,23 @@
       <c r="E60" s="33"/>
       <c r="F60" s="33"/>
       <c r="G60" s="32" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H60" s="34" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I60" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J60" s="32"/>
       <c r="K60" s="32" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L60" s="32" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M60" s="32" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N60" s="36"/>
       <c r="O60" s="36"/>
@@ -6572,13 +6886,13 @@
     </row>
     <row r="61" spans="1:31" ht="15.75" customHeight="1">
       <c r="A61" s="32" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B61" s="32" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>20</v>
@@ -6586,20 +6900,20 @@
       <c r="E61" s="33"/>
       <c r="F61" s="33"/>
       <c r="G61" s="32" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H61" s="34" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I61" s="35" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J61" s="32"/>
       <c r="K61" s="32" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L61" s="32" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M61" s="32"/>
       <c r="N61" s="36"/>
@@ -6623,13 +6937,13 @@
     </row>
     <row r="62" spans="1:31" ht="15.75" customHeight="1">
       <c r="A62" s="32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B62" s="32" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D62" s="33" t="s">
         <v>20</v>
@@ -6637,20 +6951,20 @@
       <c r="E62" s="33"/>
       <c r="F62" s="33"/>
       <c r="G62" s="32" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H62" s="34" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I62" s="35" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J62" s="32"/>
       <c r="K62" s="32" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L62" s="32" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="M62" s="32"/>
       <c r="N62" s="36"/>
@@ -6674,13 +6988,13 @@
     </row>
     <row r="63" spans="1:31" ht="15.75" customHeight="1">
       <c r="A63" s="32" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B63" s="32" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D63" s="33" t="s">
         <v>20</v>
@@ -6688,20 +7002,20 @@
       <c r="E63" s="33"/>
       <c r="F63" s="33"/>
       <c r="G63" s="32" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H63" s="34" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I63" s="35" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J63" s="32"/>
       <c r="K63" s="32" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L63" s="32" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="M63" s="32"/>
       <c r="N63" s="36"/>
@@ -6725,13 +7039,13 @@
     </row>
     <row r="64" spans="1:31" ht="15.75" customHeight="1">
       <c r="A64" s="32" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B64" s="32" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D64" s="33" t="s">
         <v>20</v>
@@ -6739,20 +7053,20 @@
       <c r="E64" s="33"/>
       <c r="F64" s="33"/>
       <c r="G64" s="32" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H64" s="34" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I64" s="35" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J64" s="32"/>
       <c r="K64" s="32" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L64" s="32" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M64" s="32"/>
       <c r="N64" s="36"/>
@@ -6776,13 +7090,13 @@
     </row>
     <row r="65" spans="1:31" ht="15.75" customHeight="1">
       <c r="A65" s="32" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B65" s="32" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D65" s="33" t="s">
         <v>20</v>
@@ -6790,20 +7104,20 @@
       <c r="E65" s="33"/>
       <c r="F65" s="33"/>
       <c r="G65" s="32" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H65" s="34" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I65" s="35" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J65" s="32"/>
       <c r="K65" s="32" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L65" s="32" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="M65" s="32"/>
       <c r="N65" s="36"/>
@@ -6827,13 +7141,13 @@
     </row>
     <row r="66" spans="1:31" ht="15.75" customHeight="1">
       <c r="A66" s="32" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B66" s="32" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C66" s="32" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D66" s="33" t="s">
         <v>20</v>
@@ -6841,19 +7155,19 @@
       <c r="E66" s="33"/>
       <c r="F66" s="33"/>
       <c r="G66" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="H66" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="I66" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="J66" s="35" t="s">
         <v>349</v>
       </c>
-      <c r="H66" s="34" t="s">
+      <c r="K66" s="32" t="s">
         <v>350</v>
-      </c>
-      <c r="I66" s="35" t="s">
-        <v>351</v>
-      </c>
-      <c r="J66" s="35" t="s">
-        <v>352</v>
-      </c>
-      <c r="K66" s="32" t="s">
-        <v>353</v>
       </c>
       <c r="L66" s="32"/>
       <c r="M66" s="32"/>
@@ -6878,13 +7192,13 @@
     </row>
     <row r="67" spans="1:31" ht="15.75" customHeight="1">
       <c r="A67" s="32" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B67" s="32" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C67" s="32" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D67" s="33" t="s">
         <v>20</v>
@@ -6892,20 +7206,20 @@
       <c r="E67" s="33"/>
       <c r="F67" s="33"/>
       <c r="G67" s="32" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H67" s="34" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I67" s="35" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J67" s="32"/>
       <c r="K67" s="32" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L67" s="32" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M67" s="32"/>
       <c r="N67" s="36"/>
@@ -6929,13 +7243,13 @@
     </row>
     <row r="68" spans="1:31" ht="15.75" customHeight="1">
       <c r="A68" s="32" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B68" s="32" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D68" s="33" t="s">
         <v>20</v>
@@ -6943,23 +7257,23 @@
       <c r="E68" s="33"/>
       <c r="F68" s="33"/>
       <c r="G68" s="32" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H68" s="34" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I68" s="35" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J68" s="32"/>
       <c r="K68" s="32" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="L68" s="32" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="M68" s="32" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="N68" s="36"/>
       <c r="O68" s="36"/>
@@ -6982,13 +7296,13 @@
     </row>
     <row r="69" spans="1:31" ht="15.75" customHeight="1">
       <c r="A69" s="32" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B69" s="32" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C69" s="32" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D69" s="33" t="s">
         <v>21</v>
@@ -6996,17 +7310,17 @@
       <c r="E69" s="33"/>
       <c r="F69" s="33"/>
       <c r="G69" s="32" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H69" s="34" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I69" s="35" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J69" s="32"/>
       <c r="K69" s="32" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="L69" s="32"/>
       <c r="M69" s="32"/>
@@ -7031,13 +7345,13 @@
     </row>
     <row r="70" spans="1:31" ht="15.75" customHeight="1">
       <c r="A70" s="32" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B70" s="32" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C70" s="32" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D70" s="33" t="s">
         <v>20</v>
@@ -7045,20 +7359,20 @@
       <c r="E70" s="33"/>
       <c r="F70" s="33"/>
       <c r="G70" s="32" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H70" s="34" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I70" s="35" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="J70" s="32"/>
       <c r="K70" s="32" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="L70" s="32" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M70" s="32"/>
       <c r="N70" s="36"/>
@@ -7082,13 +7396,13 @@
     </row>
     <row r="71" spans="1:31" ht="15.75" customHeight="1">
       <c r="A71" s="32" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B71" s="32" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D71" s="33" t="s">
         <v>20</v>
@@ -7096,21 +7410,21 @@
       <c r="E71" s="33"/>
       <c r="F71" s="33"/>
       <c r="G71" s="32" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H71" s="34" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="I71" s="35" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J71" s="32"/>
       <c r="K71" s="32" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="L71" s="32"/>
       <c r="M71" s="32" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="N71" s="36"/>
       <c r="O71" s="36"/>
@@ -7133,13 +7447,13 @@
     </row>
     <row r="72" spans="1:31" ht="15.75" customHeight="1">
       <c r="A72" s="32" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B72" s="32" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D72" s="33" t="s">
         <v>20</v>
@@ -7147,19 +7461,19 @@
       <c r="E72" s="33"/>
       <c r="F72" s="33"/>
       <c r="G72" s="32" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H72" s="34" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="I72" s="32"/>
       <c r="J72" s="32"/>
       <c r="K72" s="32" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="L72" s="32"/>
       <c r="M72" s="32" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="N72" s="36"/>
       <c r="O72" s="36"/>
@@ -7182,13 +7496,13 @@
     </row>
     <row r="73" spans="1:31" ht="15.75" customHeight="1">
       <c r="A73" s="32" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B73" s="32" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D73" s="33" t="s">
         <v>20</v>
@@ -7196,16 +7510,16 @@
       <c r="E73" s="33"/>
       <c r="F73" s="33"/>
       <c r="G73" s="32" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H73" s="34"/>
       <c r="I73" s="32"/>
       <c r="J73" s="32"/>
       <c r="K73" s="32" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="L73" s="32" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="M73" s="32"/>
       <c r="N73" s="36"/>
@@ -7229,13 +7543,13 @@
     </row>
     <row r="74" spans="1:31" ht="15.75" customHeight="1">
       <c r="A74" s="32" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B74" s="32" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D74" s="33" t="s">
         <v>20</v>
@@ -7243,17 +7557,17 @@
       <c r="E74" s="33"/>
       <c r="F74" s="33"/>
       <c r="G74" s="32" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H74" s="34" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I74" s="35" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J74" s="32"/>
       <c r="K74" s="32" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="L74" s="32"/>
       <c r="M74" s="32"/>
@@ -7278,13 +7592,13 @@
     </row>
     <row r="75" spans="1:31" ht="15.75" customHeight="1">
       <c r="A75" s="32" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D75" s="33" t="s">
         <v>20</v>
@@ -7292,17 +7606,17 @@
       <c r="E75" s="33"/>
       <c r="F75" s="33"/>
       <c r="G75" s="32" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H75" s="34" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J75" s="32"/>
       <c r="K75" s="32" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="L75" s="32"/>
       <c r="M75" s="32"/>
@@ -7327,13 +7641,13 @@
     </row>
     <row r="76" spans="1:31" ht="15.75" customHeight="1">
       <c r="A76" s="32" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B76" s="32" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D76" s="33" t="s">
         <v>21</v>
@@ -7341,15 +7655,15 @@
       <c r="E76" s="33"/>
       <c r="F76" s="33"/>
       <c r="G76" s="32" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H76" s="34"/>
       <c r="I76" s="35" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J76" s="32"/>
       <c r="K76" s="32" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L76" s="32"/>
       <c r="M76" s="32"/>
@@ -7374,13 +7688,13 @@
     </row>
     <row r="77" spans="1:31" ht="15.75" customHeight="1">
       <c r="A77" s="32" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B77" s="32" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C77" s="32" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D77" s="33" t="s">
         <v>21</v>
@@ -7388,17 +7702,17 @@
       <c r="E77" s="33"/>
       <c r="F77" s="33"/>
       <c r="G77" s="32" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H77" s="34" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J77" s="32"/>
       <c r="K77" s="32" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="L77" s="32"/>
       <c r="M77" s="32"/>
@@ -7423,13 +7737,13 @@
     </row>
     <row r="78" spans="1:31" ht="15.75" customHeight="1">
       <c r="A78" s="32" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B78" s="32" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D78" s="33" t="s">
         <v>21</v>
@@ -7437,17 +7751,17 @@
       <c r="E78" s="33"/>
       <c r="F78" s="33"/>
       <c r="G78" s="32" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H78" s="34" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="I78" s="35" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J78" s="32"/>
       <c r="K78" s="32" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="L78" s="32"/>
       <c r="M78" s="32"/>
@@ -7472,13 +7786,13 @@
     </row>
     <row r="79" spans="1:31" ht="15.75" customHeight="1">
       <c r="A79" s="32" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B79" s="32" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D79" s="33" t="s">
         <v>21</v>
@@ -7486,17 +7800,17 @@
       <c r="E79" s="33"/>
       <c r="F79" s="33"/>
       <c r="G79" s="32" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H79" s="34" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="I79" s="35" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J79" s="32"/>
       <c r="K79" s="32" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="L79" s="32"/>
       <c r="M79" s="32"/>
@@ -7521,13 +7835,13 @@
     </row>
     <row r="80" spans="1:31" ht="15.75" customHeight="1">
       <c r="A80" s="32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B80" s="32" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D80" s="33" t="s">
         <v>20</v>
@@ -7535,21 +7849,21 @@
       <c r="E80" s="33"/>
       <c r="F80" s="33"/>
       <c r="G80" s="32" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H80" s="50" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="I80" s="35" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J80" s="32"/>
       <c r="K80" s="32" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="L80" s="32"/>
       <c r="M80" s="32" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="N80" s="36"/>
       <c r="O80" s="36"/>
@@ -7572,13 +7886,13 @@
     </row>
     <row r="81" spans="1:31" ht="15.75" customHeight="1">
       <c r="A81" s="32" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B81" s="32" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C81" s="32" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D81" s="33" t="s">
         <v>20</v>
@@ -7586,23 +7900,23 @@
       <c r="E81" s="33"/>
       <c r="F81" s="33"/>
       <c r="G81" s="32" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H81" s="34" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I81" s="35" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J81" s="32"/>
       <c r="K81" s="32" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="L81" s="32" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="M81" s="51" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="N81" s="52"/>
       <c r="O81" s="52"/>
@@ -7625,13 +7939,13 @@
     </row>
     <row r="82" spans="1:31" ht="15.75" customHeight="1">
       <c r="A82" s="32" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B82" s="32" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D82" s="33" t="s">
         <v>20</v>
@@ -7639,22 +7953,22 @@
       <c r="E82" s="33"/>
       <c r="F82" s="33"/>
       <c r="G82" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="H82" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="I82" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="J82" s="35" t="s">
         <v>464</v>
       </c>
-      <c r="H82" s="34" t="s">
+      <c r="K82" s="32" t="s">
         <v>465</v>
       </c>
-      <c r="I82" s="35" t="s">
+      <c r="L82" s="32" t="s">
         <v>466</v>
-      </c>
-      <c r="J82" s="35" t="s">
-        <v>467</v>
-      </c>
-      <c r="K82" s="32" t="s">
-        <v>468</v>
-      </c>
-      <c r="L82" s="32" t="s">
-        <v>469</v>
       </c>
       <c r="M82" s="32"/>
       <c r="N82" s="36"/>
@@ -7678,13 +7992,13 @@
     </row>
     <row r="83" spans="1:31" ht="15.75" customHeight="1">
       <c r="A83" s="32" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B83" s="32" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C83" s="32" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D83" s="33" t="s">
         <v>20</v>
@@ -7692,23 +8006,23 @@
       <c r="E83" s="33"/>
       <c r="F83" s="33"/>
       <c r="G83" s="32" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H83" s="34" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J83" s="32"/>
       <c r="K83" s="32" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L83" s="32" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="M83" s="32" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="N83" s="36"/>
       <c r="O83" s="36"/>
@@ -7731,13 +8045,13 @@
     </row>
     <row r="84" spans="1:31" ht="15.75" customHeight="1">
       <c r="A84" s="32" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B84" s="32" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D84" s="33" t="s">
         <v>20</v>
@@ -7745,23 +8059,23 @@
       <c r="E84" s="33"/>
       <c r="F84" s="33"/>
       <c r="G84" s="32" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="H84" s="34" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I84" s="35" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J84" s="32"/>
       <c r="K84" s="32" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L84" s="32" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M84" s="32" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N84" s="36"/>
       <c r="O84" s="36"/>
@@ -7784,13 +8098,13 @@
     </row>
     <row r="85" spans="1:31" ht="15.75" customHeight="1">
       <c r="A85" s="32" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B85" s="32" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D85" s="33" t="s">
         <v>20</v>
@@ -7798,17 +8112,17 @@
       <c r="E85" s="33"/>
       <c r="F85" s="33"/>
       <c r="G85" s="32" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H85" s="34" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I85" s="35" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J85" s="32"/>
       <c r="K85" s="32" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="L85" s="32"/>
       <c r="M85" s="32"/>
@@ -7833,13 +8147,13 @@
     </row>
     <row r="86" spans="1:31" ht="15.75" customHeight="1">
       <c r="A86" s="32" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D86" s="33" t="s">
         <v>20</v>
@@ -7847,23 +8161,23 @@
       <c r="E86" s="33"/>
       <c r="F86" s="33"/>
       <c r="G86" s="32" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H86" s="34" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I86" s="35" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J86" s="32"/>
       <c r="K86" s="32" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="L86" s="32" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="M86" s="32" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="N86" s="36"/>
       <c r="O86" s="36"/>
@@ -7886,13 +8200,13 @@
     </row>
     <row r="87" spans="1:31" ht="15.75" customHeight="1">
       <c r="A87" s="32" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B87" s="32" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C87" s="32" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D87" s="33" t="s">
         <v>21</v>
@@ -7900,17 +8214,17 @@
       <c r="E87" s="33"/>
       <c r="F87" s="33"/>
       <c r="G87" s="32" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H87" s="34"/>
       <c r="I87" s="32"/>
       <c r="J87" s="32"/>
       <c r="K87" s="32" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L87" s="32"/>
       <c r="M87" s="32" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="N87" s="36"/>
       <c r="O87" s="36"/>
@@ -7933,13 +8247,13 @@
     </row>
     <row r="88" spans="1:31" ht="15.75" customHeight="1">
       <c r="A88" s="32" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C88" s="32" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D88" s="33" t="s">
         <v>21</v>
@@ -7947,17 +8261,17 @@
       <c r="E88" s="33"/>
       <c r="F88" s="33"/>
       <c r="G88" s="32" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H88" s="34" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I88" s="35" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J88" s="32"/>
       <c r="K88" s="32" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="L88" s="32"/>
       <c r="M88" s="32"/>
@@ -7982,13 +8296,13 @@
     </row>
     <row r="89" spans="1:31" ht="15.75" customHeight="1">
       <c r="A89" s="32" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C89" s="32" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D89" s="33" t="s">
         <v>20</v>
@@ -7996,22 +8310,22 @@
       <c r="E89" s="33"/>
       <c r="F89" s="33"/>
       <c r="G89" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="H89" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="I89" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="J89" s="35" t="s">
         <v>516</v>
       </c>
-      <c r="H89" s="34" t="s">
+      <c r="K89" s="32" t="s">
         <v>517</v>
       </c>
-      <c r="I89" s="35" t="s">
+      <c r="L89" s="32" t="s">
         <v>518</v>
-      </c>
-      <c r="J89" s="35" t="s">
-        <v>519</v>
-      </c>
-      <c r="K89" s="32" t="s">
-        <v>520</v>
-      </c>
-      <c r="L89" s="32" t="s">
-        <v>521</v>
       </c>
       <c r="M89" s="32"/>
       <c r="N89" s="36"/>
@@ -8035,13 +8349,13 @@
     </row>
     <row r="90" spans="1:31" ht="15.75" customHeight="1">
       <c r="A90" s="32" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D90" s="33" t="s">
         <v>20</v>
@@ -8049,23 +8363,23 @@
       <c r="E90" s="33"/>
       <c r="F90" s="33"/>
       <c r="G90" s="32" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H90" s="34" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I90" s="35" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J90" s="32"/>
       <c r="K90" s="32" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="L90" s="32" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="M90" s="32" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="N90" s="36"/>
       <c r="O90" s="36"/>
@@ -8088,13 +8402,13 @@
     </row>
     <row r="91" spans="1:31" ht="15.75" customHeight="1">
       <c r="A91" s="32" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D91" s="33" t="s">
         <v>20</v>
@@ -8102,20 +8416,20 @@
       <c r="E91" s="33"/>
       <c r="F91" s="33"/>
       <c r="G91" s="32" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H91" s="34" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I91" s="35" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J91" s="32"/>
       <c r="K91" s="32" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="L91" s="32" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="M91" s="32"/>
       <c r="N91" s="36"/>
@@ -8139,13 +8453,13 @@
     </row>
     <row r="92" spans="1:31" ht="15.75" customHeight="1">
       <c r="A92" s="32" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D92" s="33" t="s">
         <v>20</v>
@@ -8153,20 +8467,20 @@
       <c r="E92" s="33"/>
       <c r="F92" s="33"/>
       <c r="G92" s="32" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="H92" s="34" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="I92" s="35" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J92" s="32"/>
       <c r="K92" s="32" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L92" s="32" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="M92" s="32"/>
       <c r="N92" s="36"/>
@@ -8190,13 +8504,13 @@
     </row>
     <row r="93" spans="1:31" ht="15.75" customHeight="1">
       <c r="A93" s="32" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C93" s="32" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D93" s="33" t="s">
         <v>20</v>
@@ -8204,17 +8518,17 @@
       <c r="E93" s="33"/>
       <c r="F93" s="33"/>
       <c r="G93" s="32" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H93" s="34" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I93" s="35" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="J93" s="32"/>
       <c r="K93" s="32" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="L93" s="32"/>
       <c r="M93" s="32"/>
@@ -8239,13 +8553,13 @@
     </row>
     <row r="94" spans="1:31" ht="15.75" customHeight="1">
       <c r="A94" s="32" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C94" s="32" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D94" s="33" t="s">
         <v>20</v>
@@ -8253,17 +8567,17 @@
       <c r="E94" s="33"/>
       <c r="F94" s="33"/>
       <c r="G94" s="32" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H94" s="34" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="I94" s="35" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J94" s="32"/>
       <c r="K94" s="32" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="L94" s="32"/>
       <c r="M94" s="32"/>
@@ -8288,13 +8602,13 @@
     </row>
     <row r="95" spans="1:31" ht="15.75" customHeight="1">
       <c r="A95" s="32" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D95" s="33" t="s">
         <v>21</v>
@@ -8302,17 +8616,17 @@
       <c r="E95" s="33"/>
       <c r="F95" s="33"/>
       <c r="G95" s="32" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H95" s="34" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="I95" s="35" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J95" s="32"/>
       <c r="K95" s="32" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="L95" s="32"/>
       <c r="M95" s="32"/>
@@ -8337,13 +8651,13 @@
     </row>
     <row r="96" spans="1:31" ht="15.75" customHeight="1">
       <c r="A96" s="32" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D96" s="33" t="s">
         <v>21</v>
@@ -8351,20 +8665,20 @@
       <c r="E96" s="33"/>
       <c r="F96" s="33"/>
       <c r="G96" s="32" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H96" s="34" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="I96" s="35" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="J96" s="32"/>
       <c r="K96" s="32" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="L96" s="32" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="M96" s="32"/>
       <c r="N96" s="36"/>
@@ -8388,13 +8702,13 @@
     </row>
     <row r="97" spans="1:31" ht="15.75" customHeight="1">
       <c r="A97" s="32" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C97" s="32" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D97" s="33" t="s">
         <v>21</v>
@@ -8402,10 +8716,10 @@
       <c r="E97" s="33"/>
       <c r="F97" s="33"/>
       <c r="G97" s="32" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H97" s="34" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I97" s="32"/>
       <c r="J97" s="32"/>
@@ -8433,13 +8747,13 @@
     </row>
     <row r="98" spans="1:31" ht="15.75" customHeight="1">
       <c r="A98" s="32" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B98" s="32" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D98" s="33" t="s">
         <v>20</v>
@@ -8447,17 +8761,17 @@
       <c r="E98" s="33"/>
       <c r="F98" s="33"/>
       <c r="G98" s="32" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="H98" s="34" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J98" s="32"/>
       <c r="K98" s="32" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="L98" s="32"/>
       <c r="M98" s="32"/>
@@ -8482,13 +8796,13 @@
     </row>
     <row r="99" spans="1:31" ht="15.75" customHeight="1">
       <c r="A99" s="32" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D99" s="33" t="s">
         <v>20</v>
@@ -8497,18 +8811,18 @@
       <c r="F99" s="33"/>
       <c r="G99" s="32"/>
       <c r="H99" s="34" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="I99" s="35" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="J99" s="32"/>
       <c r="K99" s="32" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="L99" s="32"/>
       <c r="M99" s="32" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="N99" s="36"/>
       <c r="O99" s="36"/>
@@ -8531,13 +8845,13 @@
     </row>
     <row r="100" spans="1:31" ht="15.75" customHeight="1">
       <c r="A100" s="32" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C100" s="32" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D100" s="33" t="s">
         <v>20</v>
@@ -8545,17 +8859,17 @@
       <c r="E100" s="33"/>
       <c r="F100" s="33"/>
       <c r="G100" s="32" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H100" s="34" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="I100" s="35" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="J100" s="32"/>
       <c r="K100" s="32" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L100" s="32"/>
       <c r="M100" s="32"/>
@@ -8580,13 +8894,13 @@
     </row>
     <row r="101" spans="1:31" ht="15.75" customHeight="1">
       <c r="A101" s="32" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B101" s="32" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C101" s="32" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D101" s="33" t="s">
         <v>20</v>
@@ -8594,17 +8908,17 @@
       <c r="E101" s="33"/>
       <c r="F101" s="33"/>
       <c r="G101" s="32" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="H101" s="34" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="I101" s="35" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="J101" s="32"/>
       <c r="K101" s="32" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="L101" s="32"/>
       <c r="M101" s="32"/>
@@ -8629,13 +8943,13 @@
     </row>
     <row r="102" spans="1:31" ht="15.75" customHeight="1">
       <c r="A102" s="32" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B102" s="32" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C102" s="32" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D102" s="33" t="s">
         <v>20</v>
@@ -8643,23 +8957,23 @@
       <c r="E102" s="33"/>
       <c r="F102" s="33"/>
       <c r="G102" s="32" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H102" s="34" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="I102" s="35" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J102" s="32"/>
       <c r="K102" s="32" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="L102" s="32" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="M102" s="32" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="N102" s="36"/>
       <c r="O102" s="36"/>
@@ -8682,13 +8996,13 @@
     </row>
     <row r="103" spans="1:31" ht="15.75" customHeight="1">
       <c r="A103" s="32" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B103" s="32" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C103" s="32" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D103" s="33" t="s">
         <v>21</v>
@@ -8696,17 +9010,17 @@
       <c r="E103" s="33"/>
       <c r="F103" s="33"/>
       <c r="G103" s="32" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="H103" s="34" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="I103" s="35" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="J103" s="32"/>
       <c r="K103" s="32" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="L103" s="32"/>
       <c r="M103" s="32"/>
@@ -8731,13 +9045,13 @@
     </row>
     <row r="104" spans="1:31" ht="15.75" customHeight="1">
       <c r="A104" s="32" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B104" s="32" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C104" s="32" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D104" s="33" t="s">
         <v>21</v>
@@ -8745,17 +9059,17 @@
       <c r="E104" s="33"/>
       <c r="F104" s="33"/>
       <c r="G104" s="32" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="H104" s="34" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="I104" s="35" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="J104" s="32"/>
       <c r="K104" s="32" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="L104" s="32"/>
       <c r="M104" s="32"/>
@@ -8780,13 +9094,13 @@
     </row>
     <row r="105" spans="1:31" ht="15.75" customHeight="1">
       <c r="A105" s="32" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C105" s="32" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D105" s="33" t="s">
         <v>21</v>
@@ -8795,17 +9109,17 @@
       <c r="F105" s="33"/>
       <c r="G105" s="32"/>
       <c r="H105" s="34" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="I105" s="35" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J105" s="32"/>
       <c r="K105" s="32" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="L105" s="32" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M105" s="32"/>
       <c r="N105" s="36"/>
@@ -8829,13 +9143,13 @@
     </row>
     <row r="106" spans="1:31" ht="15.75" customHeight="1">
       <c r="A106" s="32" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B106" s="32" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C106" s="32" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D106" s="33" t="s">
         <v>21</v>
@@ -8843,17 +9157,17 @@
       <c r="E106" s="33"/>
       <c r="F106" s="33"/>
       <c r="G106" s="32" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="H106" s="34" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="I106" s="35" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="J106" s="32"/>
       <c r="K106" s="32" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="L106" s="32"/>
       <c r="M106" s="32"/>
@@ -8878,13 +9192,13 @@
     </row>
     <row r="107" spans="1:31" ht="15.75" customHeight="1">
       <c r="A107" s="32" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B107" s="32" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C107" s="32" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D107" s="33" t="s">
         <v>20</v>
@@ -8892,20 +9206,20 @@
       <c r="E107" s="33"/>
       <c r="F107" s="33"/>
       <c r="G107" s="32" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="H107" s="34" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I107" s="35" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="J107" s="32"/>
       <c r="K107" s="32" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="L107" s="32" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="M107" s="32"/>
       <c r="N107" s="36"/>
@@ -8929,13 +9243,13 @@
     </row>
     <row r="108" spans="1:31" ht="15.75" customHeight="1">
       <c r="A108" s="32" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B108" s="32" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C108" s="32" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D108" s="33" t="s">
         <v>20</v>
@@ -8943,23 +9257,23 @@
       <c r="E108" s="33"/>
       <c r="F108" s="33"/>
       <c r="G108" s="32" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H108" s="34" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I108" s="35" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J108" s="32"/>
       <c r="K108" s="32" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="L108" s="32" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="M108" s="32" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="N108" s="36"/>
       <c r="O108" s="36"/>
@@ -8982,13 +9296,13 @@
     </row>
     <row r="109" spans="1:31" ht="15.75" customHeight="1">
       <c r="A109" s="18" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D109" s="19" t="s">
         <v>21</v>
@@ -9000,7 +9314,7 @@
       <c r="I109" s="21"/>
       <c r="J109" s="22"/>
       <c r="K109" s="18" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="L109" s="22"/>
       <c r="M109" s="22"/>
@@ -9025,13 +9339,13 @@
     </row>
     <row r="110" spans="1:31" ht="15.75" customHeight="1">
       <c r="A110" s="18" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D110" s="19" t="s">
         <v>21</v>
@@ -9066,13 +9380,13 @@
     </row>
     <row r="111" spans="1:31" ht="15.75" customHeight="1">
       <c r="A111" s="18" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D111" s="19" t="s">
         <v>21</v>
@@ -9084,7 +9398,7 @@
       <c r="I111" s="21"/>
       <c r="J111" s="22"/>
       <c r="K111" s="18" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="L111" s="22"/>
       <c r="M111" s="22"/>
@@ -9109,7 +9423,7 @@
     </row>
     <row r="112" spans="1:31" ht="15.75" customHeight="1">
       <c r="A112" s="18" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B112" s="18"/>
       <c r="C112" s="18"/>
@@ -9146,7 +9460,7 @@
     </row>
     <row r="113" spans="1:31" ht="15.75" customHeight="1">
       <c r="A113" s="18" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="18"/>
@@ -9183,7 +9497,7 @@
     </row>
     <row r="114" spans="1:31" ht="15.75" customHeight="1">
       <c r="A114" s="18" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B114" s="18"/>
       <c r="C114" s="18"/>
@@ -9220,7 +9534,7 @@
     </row>
     <row r="115" spans="1:31" ht="15.75" customHeight="1">
       <c r="A115" s="18" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B115" s="18"/>
       <c r="C115" s="18"/>
@@ -9257,13 +9571,13 @@
     </row>
     <row r="116" spans="1:31" ht="15.75" customHeight="1">
       <c r="A116" s="32" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B116" s="32" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C116" s="32" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D116" s="33" t="s">
         <v>20</v>
@@ -9271,17 +9585,17 @@
       <c r="E116" s="33"/>
       <c r="F116" s="33"/>
       <c r="G116" s="32" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="H116" s="34" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="I116" s="35" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="J116" s="32"/>
       <c r="K116" s="32" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="L116" s="32"/>
       <c r="M116" s="32"/>
@@ -9306,13 +9620,13 @@
     </row>
     <row r="117" spans="1:31" ht="15.75" customHeight="1">
       <c r="A117" s="18" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D117" s="19" t="s">
         <v>21</v>
@@ -9324,7 +9638,7 @@
       <c r="I117" s="21"/>
       <c r="J117" s="22"/>
       <c r="K117" s="18" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="L117" s="22"/>
       <c r="M117" s="22"/>
@@ -9349,13 +9663,13 @@
     </row>
     <row r="118" spans="1:31" ht="15.75" customHeight="1">
       <c r="A118" s="32" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B118" s="32" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D118" s="33" t="s">
         <v>21</v>
@@ -9363,20 +9677,20 @@
       <c r="E118" s="33"/>
       <c r="F118" s="33"/>
       <c r="G118" s="32" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="H118" s="32" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I118" s="35" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="J118" s="32"/>
       <c r="K118" s="32" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="L118" s="32" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="M118" s="32"/>
       <c r="N118" s="36"/>
@@ -9400,13 +9714,13 @@
     </row>
     <row r="119" spans="1:31" ht="15.75" customHeight="1">
       <c r="A119" s="32" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B119" s="32" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D119" s="33" t="s">
         <v>21</v>
@@ -9414,17 +9728,17 @@
       <c r="E119" s="33"/>
       <c r="F119" s="33"/>
       <c r="G119" s="32" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I119" s="35" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J119" s="32"/>
       <c r="K119" s="32" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="L119" s="32"/>
       <c r="M119" s="32"/>
@@ -9449,13 +9763,13 @@
     </row>
     <row r="120" spans="1:31" ht="15.75" customHeight="1">
       <c r="A120" s="32" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B120" s="32" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C120" s="32" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D120" s="33" t="s">
         <v>20</v>
@@ -9463,23 +9777,23 @@
       <c r="E120" s="33"/>
       <c r="F120" s="33"/>
       <c r="G120" s="32" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H120" s="34" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="I120" s="35" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="J120" s="32"/>
       <c r="K120" s="32" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="L120" s="32" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="M120" s="32" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="N120" s="36"/>
       <c r="O120" s="36"/>
@@ -9502,13 +9816,13 @@
     </row>
     <row r="121" spans="1:31" ht="15.75" customHeight="1">
       <c r="A121" s="32" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B121" s="32" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C121" s="32" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D121" s="33" t="s">
         <v>20</v>
@@ -9516,17 +9830,17 @@
       <c r="E121" s="33"/>
       <c r="F121" s="33"/>
       <c r="G121" s="32" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H121" s="34" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="I121" s="35" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="J121" s="32"/>
       <c r="K121" s="32" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="L121" s="32"/>
       <c r="M121" s="32"/>
@@ -9551,10 +9865,10 @@
     </row>
     <row r="122" spans="1:31" ht="15.75" customHeight="1">
       <c r="A122" s="32" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B122" s="32" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C122" s="32" t="s">
         <v>79</v>
@@ -9565,19 +9879,19 @@
       <c r="E122" s="33"/>
       <c r="F122" s="33"/>
       <c r="G122" s="32" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H122" s="34" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="I122" s="32"/>
       <c r="J122" s="32"/>
       <c r="K122" s="32" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="L122" s="32"/>
       <c r="M122" s="32" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="N122" s="36"/>
       <c r="O122" s="36"/>
@@ -9600,10 +9914,10 @@
     </row>
     <row r="123" spans="1:31" ht="15.75" customHeight="1">
       <c r="A123" s="32" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B123" s="32" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C123" s="32" t="s">
         <v>69</v>
@@ -9614,13 +9928,13 @@
       <c r="E123" s="33"/>
       <c r="F123" s="33"/>
       <c r="G123" s="32" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="H123" s="34" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="I123" s="35" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J123" s="32"/>
       <c r="K123" s="32"/>
@@ -9647,13 +9961,13 @@
     </row>
     <row r="124" spans="1:31" ht="15.75" customHeight="1">
       <c r="A124" s="32" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B124" s="32" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C124" s="32" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D124" s="33" t="s">
         <v>20</v>
@@ -9661,21 +9975,21 @@
       <c r="E124" s="33"/>
       <c r="F124" s="33"/>
       <c r="G124" s="32" t="s">
+        <v>722</v>
+      </c>
+      <c r="H124" s="34" t="s">
+        <v>723</v>
+      </c>
+      <c r="I124" s="35" t="s">
+        <v>724</v>
+      </c>
+      <c r="J124" s="35" t="s">
         <v>725</v>
-      </c>
-      <c r="H124" s="34" t="s">
-        <v>726</v>
-      </c>
-      <c r="I124" s="35" t="s">
-        <v>727</v>
-      </c>
-      <c r="J124" s="35" t="s">
-        <v>728</v>
       </c>
       <c r="K124" s="32"/>
       <c r="L124" s="32"/>
       <c r="M124" s="32" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="N124" s="36"/>
       <c r="O124" s="36"/>
@@ -9698,13 +10012,13 @@
     </row>
     <row r="125" spans="1:31" ht="15.75" customHeight="1">
       <c r="A125" s="32" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B125" s="32" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C125" s="32" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D125" s="33" t="s">
         <v>20</v>
@@ -9712,17 +10026,17 @@
       <c r="E125" s="33"/>
       <c r="F125" s="33"/>
       <c r="G125" s="32" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="H125" s="34" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I125" s="35" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="J125" s="32"/>
       <c r="K125" s="32" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="L125" s="32"/>
       <c r="M125" s="32"/>
@@ -9747,13 +10061,13 @@
     </row>
     <row r="126" spans="1:31" ht="15.75" customHeight="1">
       <c r="A126" s="32" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B126" s="32" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C126" s="32" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D126" s="33" t="s">
         <v>20</v>
@@ -9761,17 +10075,17 @@
       <c r="E126" s="33"/>
       <c r="F126" s="33"/>
       <c r="G126" s="32" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="H126" s="34" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="I126" s="35" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="J126" s="32"/>
       <c r="K126" s="32" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="L126" s="32"/>
       <c r="M126" s="32"/>
@@ -9796,13 +10110,13 @@
     </row>
     <row r="127" spans="1:31" ht="15.75" customHeight="1">
       <c r="A127" s="32" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B127" s="32" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C127" s="32" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D127" s="33" t="s">
         <v>21</v>
@@ -9810,18 +10124,18 @@
       <c r="E127" s="33"/>
       <c r="F127" s="33"/>
       <c r="G127" s="32" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="H127" s="34" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I127" s="32"/>
       <c r="J127" s="32"/>
       <c r="K127" s="32" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L127" s="32" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="M127" s="32"/>
       <c r="N127" s="36"/>
@@ -9845,13 +10159,13 @@
     </row>
     <row r="128" spans="1:31" ht="15.75" customHeight="1">
       <c r="A128" s="32" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B128" s="32" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C128" s="32" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D128" s="33" t="s">
         <v>20</v>
@@ -9859,20 +10173,20 @@
       <c r="E128" s="33"/>
       <c r="F128" s="33"/>
       <c r="G128" s="32" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="H128" s="34" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I128" s="35" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="J128" s="32"/>
       <c r="K128" s="32" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="L128" s="32" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="M128" s="32"/>
       <c r="N128" s="36"/>
@@ -9896,13 +10210,13 @@
     </row>
     <row r="129" spans="1:31" ht="15.75" customHeight="1">
       <c r="A129" s="32" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B129" s="32" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C129" s="32" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D129" s="33" t="s">
         <v>20</v>
@@ -9910,21 +10224,21 @@
       <c r="E129" s="33"/>
       <c r="F129" s="33"/>
       <c r="G129" s="32" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="H129" s="34" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="I129" s="35" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="J129" s="32"/>
       <c r="K129" s="32" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="L129" s="32"/>
       <c r="M129" s="32" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="N129" s="36"/>
       <c r="O129" s="36"/>
@@ -9947,13 +10261,13 @@
     </row>
     <row r="130" spans="1:31" ht="15.75" customHeight="1">
       <c r="A130" s="32" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B130" s="32" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C130" s="32" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D130" s="33" t="s">
         <v>20</v>
@@ -9961,23 +10275,23 @@
       <c r="E130" s="33"/>
       <c r="F130" s="33"/>
       <c r="G130" s="32" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="H130" s="34" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="I130" s="35" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="J130" s="32"/>
       <c r="K130" s="32" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L130" s="32" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="M130" s="32" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="N130" s="36"/>
       <c r="O130" s="36"/>
@@ -10000,13 +10314,13 @@
     </row>
     <row r="131" spans="1:31" ht="15.75" customHeight="1">
       <c r="A131" s="32" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B131" s="32" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C131" s="32" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D131" s="33" t="s">
         <v>20</v>
@@ -10014,23 +10328,23 @@
       <c r="E131" s="33"/>
       <c r="F131" s="33"/>
       <c r="G131" s="32" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="H131" s="34" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="I131" s="35" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="J131" s="32"/>
       <c r="K131" s="32" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="L131" s="32" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="M131" s="32" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="N131" s="36"/>
       <c r="O131" s="36"/>
@@ -10053,13 +10367,13 @@
     </row>
     <row r="132" spans="1:31" ht="15.75" customHeight="1">
       <c r="A132" s="32" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B132" s="32" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C132" s="32" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D132" s="33" t="s">
         <v>20</v>
@@ -10067,23 +10381,23 @@
       <c r="E132" s="33"/>
       <c r="F132" s="33"/>
       <c r="G132" s="32" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="H132" s="34" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="I132" s="35" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="J132" s="32"/>
       <c r="K132" s="32" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="L132" s="32" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="M132" s="32" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="N132" s="36"/>
       <c r="O132" s="36"/>
@@ -10109,10 +10423,10 @@
         <v>48</v>
       </c>
       <c r="B133" s="32" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C133" s="32" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D133" s="33" t="s">
         <v>20</v>
@@ -10120,23 +10434,23 @@
       <c r="E133" s="33"/>
       <c r="F133" s="33"/>
       <c r="G133" s="32" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="H133" s="34" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="I133" s="35" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="J133" s="32"/>
       <c r="K133" s="32" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="L133" s="32" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="M133" s="32" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="N133" s="36"/>
       <c r="O133" s="36"/>
@@ -10159,13 +10473,13 @@
     </row>
     <row r="134" spans="1:31" ht="15.75" customHeight="1">
       <c r="A134" s="32" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B134" s="32" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C134" s="32" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D134" s="33" t="s">
         <v>20</v>
@@ -10173,20 +10487,20 @@
       <c r="E134" s="33"/>
       <c r="F134" s="33"/>
       <c r="G134" s="32" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="H134" s="34" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="I134" s="35" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="J134" s="32"/>
       <c r="K134" s="32" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="L134" s="32" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="M134" s="32"/>
       <c r="N134" s="36"/>
@@ -10210,13 +10524,13 @@
     </row>
     <row r="135" spans="1:31" ht="15.75" customHeight="1">
       <c r="A135" s="32" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B135" s="32" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C135" s="32" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D135" s="33" t="s">
         <v>20</v>
@@ -10224,13 +10538,13 @@
       <c r="E135" s="33"/>
       <c r="F135" s="33"/>
       <c r="G135" s="32" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="H135" s="34" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="I135" s="35" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="J135" s="32"/>
       <c r="K135" s="32"/>
@@ -10257,13 +10571,13 @@
     </row>
     <row r="136" spans="1:31" ht="15.75" customHeight="1">
       <c r="A136" s="32" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B136" s="32" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C136" s="32" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D136" s="33" t="s">
         <v>20</v>
@@ -10271,17 +10585,17 @@
       <c r="E136" s="33"/>
       <c r="F136" s="33"/>
       <c r="G136" s="32" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="H136" s="34" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="I136" s="35" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="J136" s="32"/>
       <c r="K136" s="32" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="L136" s="32"/>
       <c r="M136" s="32"/>
@@ -10306,13 +10620,13 @@
     </row>
     <row r="137" spans="1:31" ht="15.75" customHeight="1">
       <c r="A137" s="32" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B137" s="32" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C137" s="32" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D137" s="33" t="s">
         <v>20</v>
@@ -10320,17 +10634,17 @@
       <c r="E137" s="33"/>
       <c r="F137" s="33"/>
       <c r="G137" s="32" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="H137" s="34" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="I137" s="35" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="J137" s="32"/>
       <c r="K137" s="32" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="L137" s="32"/>
       <c r="M137" s="32"/>
@@ -10355,13 +10669,13 @@
     </row>
     <row r="138" spans="1:31" ht="15.75" customHeight="1">
       <c r="A138" s="32" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B138" s="32" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C138" s="32" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D138" s="33" t="s">
         <v>20</v>
@@ -10369,23 +10683,23 @@
       <c r="E138" s="33"/>
       <c r="F138" s="33"/>
       <c r="G138" s="32" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="H138" s="32" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="I138" s="35" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="J138" s="32"/>
       <c r="K138" s="32" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="L138" s="32" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="M138" s="51" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="N138" s="52"/>
       <c r="O138" s="52"/>
@@ -10408,13 +10722,13 @@
     </row>
     <row r="139" spans="1:31" ht="15.75" customHeight="1">
       <c r="A139" s="32" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B139" s="32" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C139" s="32" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D139" s="33" t="s">
         <v>21</v>
@@ -10422,21 +10736,21 @@
       <c r="E139" s="33"/>
       <c r="F139" s="33"/>
       <c r="G139" s="32" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="H139" s="34" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="I139" s="35" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="J139" s="32"/>
       <c r="K139" s="32" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="L139" s="32"/>
       <c r="M139" s="32" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="N139" s="36"/>
       <c r="O139" s="36"/>
@@ -10459,13 +10773,13 @@
     </row>
     <row r="140" spans="1:31" ht="15.75" customHeight="1">
       <c r="A140" s="32" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B140" s="32" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C140" s="32" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D140" s="33" t="s">
         <v>21</v>
@@ -10473,15 +10787,15 @@
       <c r="E140" s="33"/>
       <c r="F140" s="33"/>
       <c r="G140" s="32" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="H140" s="34"/>
       <c r="I140" s="35" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="J140" s="32"/>
       <c r="K140" s="32" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="L140" s="32"/>
       <c r="M140" s="32"/>
@@ -10506,13 +10820,13 @@
     </row>
     <row r="141" spans="1:31" ht="15.75" customHeight="1">
       <c r="A141" s="32" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B141" s="32" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C141" s="32" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D141" s="33" t="s">
         <v>21</v>
@@ -10520,15 +10834,15 @@
       <c r="E141" s="33"/>
       <c r="F141" s="33"/>
       <c r="G141" s="32" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="H141" s="34" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="I141" s="35"/>
       <c r="J141" s="32"/>
       <c r="K141" s="32" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="L141" s="32"/>
       <c r="M141" s="32"/>
@@ -10553,13 +10867,13 @@
     </row>
     <row r="142" spans="1:31" ht="15.75" customHeight="1">
       <c r="A142" s="32" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B142" s="32" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C142" s="32" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D142" s="33" t="s">
         <v>21</v>
@@ -10567,17 +10881,17 @@
       <c r="E142" s="33"/>
       <c r="F142" s="33"/>
       <c r="G142" s="32" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="H142" s="34" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="I142" s="35" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="J142" s="32"/>
       <c r="K142" s="32" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="L142" s="32"/>
       <c r="M142" s="32"/>
@@ -10602,13 +10916,13 @@
     </row>
     <row r="143" spans="1:31" ht="15.75" customHeight="1">
       <c r="A143" s="32" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B143" s="32" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C143" s="32" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D143" s="33" t="s">
         <v>20</v>
@@ -10616,19 +10930,19 @@
       <c r="E143" s="33"/>
       <c r="F143" s="33"/>
       <c r="G143" s="32" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="H143" s="34"/>
       <c r="I143" s="35" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="J143" s="32"/>
       <c r="K143" s="32"/>
       <c r="L143" s="32" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="M143" s="32" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="N143" s="36"/>
       <c r="O143" s="36"/>
@@ -10651,13 +10965,13 @@
     </row>
     <row r="144" spans="1:31" ht="15.75" customHeight="1">
       <c r="A144" s="32" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B144" s="32" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="C144" s="32" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D144" s="33" t="s">
         <v>20</v>
@@ -10665,20 +10979,20 @@
       <c r="E144" s="33"/>
       <c r="F144" s="33"/>
       <c r="G144" s="32" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="H144" s="34" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="I144" s="35" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="J144" s="32"/>
       <c r="K144" s="32" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="L144" s="32" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="M144" s="32"/>
       <c r="N144" s="36"/>
@@ -10702,13 +11016,13 @@
     </row>
     <row r="145" spans="1:31" ht="15.75" customHeight="1">
       <c r="A145" s="32" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B145" s="32" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C145" s="32" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D145" s="33" t="s">
         <v>20</v>
@@ -10716,17 +11030,17 @@
       <c r="E145" s="33"/>
       <c r="F145" s="33"/>
       <c r="G145" s="32" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="H145" s="34" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="I145" s="35" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="J145" s="32"/>
       <c r="K145" s="32" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="L145" s="32"/>
       <c r="M145" s="32"/>
@@ -10751,13 +11065,13 @@
     </row>
     <row r="146" spans="1:31" ht="15.75" customHeight="1">
       <c r="A146" s="32" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B146" s="32" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C146" s="32" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D146" s="33" t="s">
         <v>20</v>
@@ -10765,17 +11079,17 @@
       <c r="E146" s="33"/>
       <c r="F146" s="33"/>
       <c r="G146" s="32" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="H146" s="34" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="I146" s="35" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="J146" s="32"/>
       <c r="K146" s="32" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="L146" s="32"/>
       <c r="M146" s="32"/>
@@ -10800,13 +11114,13 @@
     </row>
     <row r="147" spans="1:31" ht="15.75" customHeight="1">
       <c r="A147" s="32" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B147" s="32" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C147" s="32" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D147" s="33" t="s">
         <v>20</v>
@@ -10814,15 +11128,15 @@
       <c r="E147" s="33"/>
       <c r="F147" s="33"/>
       <c r="G147" s="32" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="H147" s="34" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="I147" s="32"/>
       <c r="J147" s="32"/>
       <c r="K147" s="32" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="L147" s="32"/>
       <c r="M147" s="32"/>
@@ -10847,13 +11161,13 @@
     </row>
     <row r="148" spans="1:31" ht="15.75" customHeight="1">
       <c r="A148" s="32" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B148" s="32" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C148" s="32" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D148" s="33" t="s">
         <v>20</v>
@@ -10861,18 +11175,18 @@
       <c r="E148" s="33"/>
       <c r="F148" s="33"/>
       <c r="G148" s="32" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="H148" s="34" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="I148" s="32"/>
       <c r="J148" s="32"/>
       <c r="K148" s="32" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="L148" s="32" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="M148" s="32"/>
       <c r="N148" s="36"/>
@@ -10896,13 +11210,13 @@
     </row>
     <row r="149" spans="1:31" ht="15.75" customHeight="1">
       <c r="A149" s="32" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B149" s="32" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C149" s="32" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D149" s="33" t="s">
         <v>20</v>
@@ -10910,25 +11224,25 @@
       <c r="E149" s="33"/>
       <c r="F149" s="33"/>
       <c r="G149" s="32" t="s">
+        <v>890</v>
+      </c>
+      <c r="H149" s="34" t="s">
+        <v>891</v>
+      </c>
+      <c r="I149" s="35" t="s">
+        <v>892</v>
+      </c>
+      <c r="J149" s="35" t="s">
         <v>893</v>
       </c>
-      <c r="H149" s="34" t="s">
+      <c r="K149" s="32" t="s">
         <v>894</v>
       </c>
-      <c r="I149" s="35" t="s">
+      <c r="L149" s="32" t="s">
         <v>895</v>
       </c>
-      <c r="J149" s="35" t="s">
+      <c r="M149" s="32" t="s">
         <v>896</v>
-      </c>
-      <c r="K149" s="32" t="s">
-        <v>897</v>
-      </c>
-      <c r="L149" s="32" t="s">
-        <v>898</v>
-      </c>
-      <c r="M149" s="32" t="s">
-        <v>899</v>
       </c>
       <c r="N149" s="36"/>
       <c r="O149" s="36"/>
@@ -10951,13 +11265,13 @@
     </row>
     <row r="150" spans="1:31" ht="15.75" customHeight="1">
       <c r="A150" s="32" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B150" s="32" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C150" s="32" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D150" s="33" t="s">
         <v>20</v>
@@ -10965,23 +11279,23 @@
       <c r="E150" s="33"/>
       <c r="F150" s="33"/>
       <c r="G150" s="32" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="H150" s="34" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="I150" s="35" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="J150" s="32"/>
       <c r="K150" s="32" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="L150" s="32" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="M150" s="32" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="N150" s="36"/>
       <c r="O150" s="36"/>
@@ -11004,13 +11318,13 @@
     </row>
     <row r="151" spans="1:31" ht="15.75" customHeight="1">
       <c r="A151" s="32" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B151" s="32" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C151" s="32" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D151" s="33" t="s">
         <v>20</v>
@@ -11018,19 +11332,19 @@
       <c r="E151" s="33"/>
       <c r="F151" s="33"/>
       <c r="G151" s="32" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="H151" s="34"/>
       <c r="I151" s="35" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="J151" s="32"/>
       <c r="K151" s="32" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="L151" s="32"/>
       <c r="M151" s="32" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="N151" s="36"/>
       <c r="O151" s="36"/>
@@ -11053,13 +11367,13 @@
     </row>
     <row r="152" spans="1:31" ht="15.75" customHeight="1">
       <c r="A152" s="32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B152" s="32" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C152" s="32" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D152" s="33" t="s">
         <v>20</v>
@@ -11067,15 +11381,15 @@
       <c r="E152" s="33"/>
       <c r="F152" s="33"/>
       <c r="G152" s="32" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="H152" s="34" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="I152" s="32"/>
       <c r="J152" s="32"/>
       <c r="K152" s="32" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="L152" s="32"/>
       <c r="M152" s="32"/>
@@ -11100,13 +11414,13 @@
     </row>
     <row r="153" spans="1:31" ht="15.75" customHeight="1">
       <c r="A153" s="32" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B153" s="32" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="D153" s="33" t="s">
         <v>21</v>
@@ -11114,17 +11428,17 @@
       <c r="E153" s="33"/>
       <c r="F153" s="33"/>
       <c r="G153" s="32" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="H153" s="34" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="I153" s="35" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="J153" s="32"/>
       <c r="K153" s="32" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="L153" s="32"/>
       <c r="M153" s="32"/>
@@ -40644,9 +40958,21 @@
     <hyperlink ref="L16" r:id="rId123"/>
     <hyperlink ref="M16" r:id="rId124"/>
     <hyperlink ref="P16" r:id="rId125"/>
+    <hyperlink ref="P17" r:id="rId126"/>
+    <hyperlink ref="L17" r:id="rId127"/>
+    <hyperlink ref="P18" r:id="rId128"/>
+    <hyperlink ref="P19" r:id="rId129"/>
+    <hyperlink ref="L20" r:id="rId130"/>
+    <hyperlink ref="P20" r:id="rId131"/>
+    <hyperlink ref="L22" r:id="rId132"/>
+    <hyperlink ref="M22" r:id="rId133"/>
+    <hyperlink ref="P25" r:id="rId134"/>
+    <hyperlink ref="M26" r:id="rId135"/>
+    <hyperlink ref="P29" r:id="rId136"/>
+    <hyperlink ref="P30" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId126"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId138"/>
 </worksheet>
 </file>
 
